--- a/configs/microservice/bff-service/static/docs/users.xlsx
+++ b/configs/microservice/bff-service/static/docs/users.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>用户名</t>
   </si>
@@ -35,16 +35,13 @@
     <t>密码</t>
   </si>
   <si>
-    <t>单位</t>
+    <t>邮箱</t>
   </si>
   <si>
     <t>电话</t>
   </si>
   <si>
     <t>角色</t>
-  </si>
-  <si>
-    <t>备注</t>
   </si>
 </sst>
 </file>
@@ -1189,10 +1186,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="5"/>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="4"/>
+  <cols>
+    <col min="2" max="2" width="19.2727272727273" customWidth="1"/>
+    <col min="3" max="3" width="17.3636363636364" customWidth="1"/>
+    <col min="4" max="4" width="17.1818181818182" customWidth="1"/>
+    <col min="5" max="5" width="13.7272727272727" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1208,9 +1211,6 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
